--- a/evaluation/cuestionarios_participante.xlsx
+++ b/evaluation/cuestionarios_participante.xlsx
@@ -737,10 +737,10 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>No importa la redacción: puedes escribir oraciones o una lista de ideas. Si de una página no recuerdas nada, escribe «No recuerdo».</t>
+          <t>Las páginas están en el orden en que las leíste: la página web 1 es la primera. No importa la redacción: oraciones o una lista de ideas. Si de una página no recuerdas nada, escribe «No recuerdo».</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
@@ -764,7 +764,7 @@
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Página web: «El hielo del planeta se está derritiendo»</t>
+          <t>Página web 1 (la primera que leíste)</t>
         </is>
       </c>
       <c r="B9" s="9" t="n"/>
@@ -791,7 +791,7 @@
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Página web: «Cambio climático: causas y evidencia observacional»</t>
+          <t>Página web 2 (la segunda que leíste)</t>
         </is>
       </c>
       <c r="B15" s="9" t="n"/>
@@ -818,7 +818,7 @@
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Página web: «Forzamiento radiativo y sensibilidad climática»</t>
+          <t>Página web 3 (la tercera que leíste)</t>
         </is>
       </c>
       <c r="B21" s="9" t="n"/>
@@ -1861,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1893,7 +1893,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Versión 3.0 — 29/09/2026</t>
+          <t>Basado en el Anexo 4 del protocolo (v3.0, 29/09/2026), adaptado a la lectura</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="42" t="inlineStr">
         <is>
-          <t>Considerando los 2 métodos, ¿cuál te pareció el más rápido? Por favor, ordénalos.</t>
+          <t>Considerando los 2 métodos, ¿con cuál la ayuda llegó en mejor momento? Por favor, ordénalos.</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>¿Con cuál crees que cometiste menos errores (en orden)?</t>
+          <t>¿Con cuál método entendiste mejor el contenido (en orden)?</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="42" t="inlineStr">
         <is>
-          <t>Si tuvieras que usar un solo método para comunicarte, ¿cuál elegirías? Por favor, ordena:</t>
+          <t>Si tuvieras que leer textos difíciles con un solo método, ¿cuál elegirías? Por favor, ordena:</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B44" s="40" t="inlineStr">
         <is>
-          <t>¿En qué medida la técnica te permitió mejorar tu rendimiento?</t>
+          <t>¿En qué medida el método te ayudó a entender el texto?</t>
         </is>
       </c>
       <c r="C44" s="27" t="n"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="B45" s="41" t="inlineStr">
         <is>
-          <t>¿Hasta qué punto la técnica ha permitido una reducción en el número de errores cometidos?</t>
+          <t>¿Qué tan útiles fueron las explicaciones que recibiste?</t>
         </is>
       </c>
       <c r="C45" s="27" t="n"/>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B46" s="40" t="inlineStr">
         <is>
-          <t>¿En qué nivel resultaban más agradables de usar las interfaces con la técnica?</t>
+          <t>¿Qué tan agradable fue leer con este método?</t>
         </is>
       </c>
       <c r="C46" s="27" t="n"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B47" s="41" t="inlineStr">
         <is>
-          <t>¿Qué tan fácil fue aprender a utilizar esta técnica?</t>
+          <t>¿Qué tan fácil fue aprender a utilizar este método?</t>
         </is>
       </c>
       <c r="C47" s="27" t="n"/>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B48" s="40" t="inlineStr">
         <is>
-          <t>¿Qué tan precisa percibiste la técnica durante la interacción?</t>
+          <t>¿Con qué frecuencia la ayuda apareció cuando de verdad la necesitabas?</t>
         </is>
       </c>
       <c r="C48" s="27" t="n"/>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B49" s="41" t="inlineStr">
         <is>
-          <t>¿Qué nivel de confianza sentiste al utilizar esta técnica?</t>
+          <t>¿Qué nivel de confianza sentiste al utilizar este método?</t>
         </is>
       </c>
       <c r="C49" s="27" t="n"/>
@@ -2235,91 +2235,103 @@
       </c>
       <c r="B50" s="40" t="inlineStr">
         <is>
-          <t>¿Qué tan dispuesto(a) estarías a utilizar esta técnica en tu vida diaria?</t>
+          <t>¿Qué tan dispuesto(a) estarías a utilizar este método en tu vida diaria al leer en internet?</t>
         </is>
       </c>
       <c r="C50" s="27" t="n"/>
       <c r="D50" s="27" t="n"/>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>¿Qué tanto te distrajo o interrumpió la ayuda?</t>
+        </is>
+      </c>
+      <c r="C51" s="27" t="n"/>
+      <c r="D51" s="27" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Comentarios finales</t>
         </is>
       </c>
-      <c r="B52" s="9" t="n"/>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>¿Qué aspectos positivos encontraste en cada técnica?</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="70" customHeight="1">
-      <c r="A55" s="11" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>¿Qué aspectos positivos encontraste en cada método?</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="11" t="n"/>
+      <c r="B56" s="12" t="n"/>
+      <c r="C56" s="12" t="n"/>
+      <c r="D56" s="12" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
         <is>
           <t>¿Qué dificultades encontraste?</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="70" customHeight="1">
-      <c r="A58" s="11" t="n"/>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>¿Tienes alguna sugerencia para mejorar las técnicas evaluadas?</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="70" customHeight="1">
-      <c r="A61" s="11" t="n"/>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
+    <row r="59" ht="70" customHeight="1">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>¿Tienes alguna sugerencia para mejorar los métodos evaluados?</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="70" customHeight="1">
+      <c r="A62" s="11" t="n"/>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="B13:D13"/>
-    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C18 C19 C22 C23 C26 C27 C30 C31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"1 = Primer lugar,2 = Segundo lugar"</formula1>
     </dataValidation>
-    <dataValidation sqref="C44 C45 C46 C47 C48 C49 C50 D44 D45 D46 D47 D48 D49 D50" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="C44 C45 C46 C47 C48 C49 C50 C51 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"1 = Muy bajo,2 = Bajo,3 = Medio,4 = Alto,5 = Muy alto"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2335,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,7 +2953,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>orden_rapido_m1</t>
+          <t>orden_momento_m1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2958,7 +2970,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>orden_rapido_m2</t>
+          <t>orden_momento_m2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3009,7 +3021,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>orden_errores_m1</t>
+          <t>orden_comprension_m1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3026,7 +3038,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>orden_errores_m2</t>
+          <t>orden_comprension_m2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3077,7 +3089,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>califica_rendimiento_m1</t>
+          <t>califica_entender_m1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,7 +3106,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>califica_rendimiento_m2</t>
+          <t>califica_entender_m2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3111,7 +3123,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>califica_menos_errores_m1</t>
+          <t>califica_utilidad_m1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3128,7 +3140,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>califica_menos_errores_m2</t>
+          <t>califica_utilidad_m2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3213,7 +3225,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>califica_precision_m1</t>
+          <t>califica_oportuna_m1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3230,7 +3242,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>califica_precision_m2</t>
+          <t>califica_oportuna_m2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3315,12 +3327,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>comentario_positivos</t>
+          <t>califica_distraccion_m1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>A55</t>
+          <t>C51</t>
         </is>
       </c>
     </row>
@@ -3332,12 +3344,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>comentario_dificultades</t>
+          <t>califica_distraccion_m2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>D51</t>
         </is>
       </c>
     </row>
@@ -3349,12 +3361,46 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
+          <t>comentario_positivos</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>A56</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>comentario_dificultades</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A59</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>comentario_sugerencias</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>A61</t>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A62</t>
         </is>
       </c>
     </row>

--- a/evaluation/cuestionarios_participante.xlsx
+++ b/evaluation/cuestionarios_participante.xlsx
@@ -2,26 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Comprensión" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NASA-TLX" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SUS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NASA-TLX Método 1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="NASA-TLX Método 2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Post-experimento" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="_mapa" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +31,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="16"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -52,19 +51,30 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00404040"/>
+      <color rgb="FF404040"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00606060"/>
+      <color rgb="FF606060"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="12">
@@ -76,56 +86,56 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EAF1FB"/>
+        <fgColor rgb="FFEAF1FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E75B6"/>
+        <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F9FC"/>
+        <fgColor rgb="FFF7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="FFF8CBAD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFC6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFEDEDED"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -135,42 +145,105 @@
     </border>
     <border>
       <left style="thick">
-        <color rgb="002E75B6"/>
+        <color rgb="FF2E75B6"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="00BF9000"/>
+        <color rgb="FFBF9000"/>
       </left>
       <right style="medium">
-        <color rgb="00BF9000"/>
+        <color rgb="FFBF9000"/>
       </right>
       <top style="medium">
-        <color rgb="00BF9000"/>
+        <color rgb="FFBF9000"/>
       </top>
       <bottom style="medium">
-        <color rgb="00BF9000"/>
+        <color rgb="FFBF9000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </left>
       <right style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBF9000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFBF9000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFBF9000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFBF9000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -178,63 +251,136 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </right>
       <top style="thin">
-        <color rgb="00A6A6A6"/>
+        <color rgb="FFA6A6A6"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00A6A6A6"/>
-      </right>
-      <top style="thin">
-        <color rgb="00A6A6A6"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00A6A6A6"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -245,88 +391,10 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" indent="2"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -686,161 +754,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
+    <tabColor rgb="FF2E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" style="28" min="1" max="1"/>
+    <col width="30" customWidth="1" style="28" min="2" max="2"/>
+    <col width="16" customWidth="1" style="28" min="3" max="4"/>
+    <col width="13" customWidth="1" style="28" min="5" max="5"/>
+    <col width="16" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>Lo que entendiste de cada página web</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Hoja 1 de 4 · Comprensión</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+    </row>
+    <row r="4" ht="33.95" customHeight="1" s="28">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>Sin volver a las páginas web, escribe en cada recuadro amarillo, con tus propias palabras, lo que entendiste de esa página: las ideas principales y los detalles que recuerdes.</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    </row>
+    <row r="5" ht="44.1" customHeight="1" s="28">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Las páginas están en el orden en que las leíste: la página web 1 es la primera. No importa la redacción: oraciones o una lista de ideas. Si de una página no recuerdas nada, escribe «No recuerdo».</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+    </row>
+    <row r="6" ht="30" customHeight="1" s="28">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>Cómo escribir: haz clic en el recuadro y escribe. Para pasar a otra línea dentro del recuadro usa Alt + Enter. Al terminar, pulsa Enter o haz clic fuera del recuadro.</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    </row>
+    <row r="9" ht="26.1" customHeight="1" s="28">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>Página web 1 (la primera que leíste)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>¿Qué entendiste de esta página web?</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="260" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="12" ht="260.1" customHeight="1" s="28">
+      <c r="A12" s="33" t="n"/>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="35" t="n"/>
+    </row>
+    <row r="15" ht="26.1" customHeight="1" s="28">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>Página web 2 (la segunda que leíste)</t>
         </is>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="31" t="inlineStr">
         <is>
           <t>¿Qué entendiste de esta página web?</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="260" customHeight="1">
-      <c r="A18" s="11" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="18" ht="260.1" customHeight="1" s="28">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="35" t="n"/>
+    </row>
+    <row r="21" ht="26.1" customHeight="1" s="28">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>Página web 3 (la tercera que leíste)</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="31" t="inlineStr">
         <is>
           <t>¿Qué entendiste de esta página web?</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="260" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
+    <row r="24" ht="260.1" customHeight="1" s="28">
+      <c r="A24" s="33" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -861,7 +888,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup fitToHeight="0"/>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="13" min="0" max="16383" man="1"/>
     <brk id="19" min="0" max="16383" man="1"/>
@@ -872,1472 +899,1868 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
+    <tabColor rgb="FF7030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" style="28" min="1" max="1"/>
+    <col width="22" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="20" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="46" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cuestionario NASA-TLX</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Cuestionario NASA-TLX · Método 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Hoja 2 de 4 · Carga de trabajo</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    </row>
+    <row r="4" ht="30" customHeight="1" s="28">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Cómo responder: haz clic en una celda amarilla y elige tu respuesta en la flecha ▼ que aparece a la derecha.</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Responde pensando en TODA la tarea: la lectura de las 3 páginas web.</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+    </row>
+    <row r="5" ht="33.95" customHeight="1" s="28">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Responde pensando SOLO en la lectura con el Método 1: Ayuda automática: la ayuda apareció sola cuando el sistema detectó que te costaba leer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.95" customHeight="1" s="28">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>No pienses en las otras páginas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Cuestionario NASA-TLX aplicado al proyecto IRIS · Versión 3.0 — 29/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="10" ht="26.1" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>Parte 1 · ¿Cuánto te exigió la tarea?</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+    </row>
+    <row r="12" ht="45.95" customHeight="1" s="28">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>Por favor, lea cuidadosamente la descripción de cada dimensión y seleccione el nivel que mejor represente su experiencia durante la realización de la tarea. Preste especial atención al significado de cada extremo de la escala.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="13" ht="32.1" customHeight="1" s="28">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>La escala va de 0 a 100 en pasos de 5: 0 es el extremo izquierdo y 100 el derecho. Ojo: en «Desempeño» la escala va al revés (0 = Muy bueno, 100 = Muy malo).</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="B14" s="16" t="inlineStr">
+    <row r="15" ht="32.1" customHeight="1" s="28">
+      <c r="B15" s="44" t="inlineStr">
         <is>
           <t>Dimensión</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C15" s="44" t="inlineStr">
         <is>
           <t>Si eliges 0</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D15" s="44" t="inlineStr">
         <is>
           <t>Tu nivel
 (0 a 100)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E15" s="44" t="inlineStr">
         <is>
           <t>Si eliges 100</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F15" s="44" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+    <row r="16" ht="44.1" customHeight="1" s="28">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
-      <c r="F15" s="20" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Cantidad de actividad mental y perceptiva que la tarea exige (decidir, pensar, calcular, procurar, etc.).</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="B16" s="21" t="inlineStr">
+    <row r="17" ht="44.1" customHeight="1" s="28">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Cantidad de actividad física que la tarea exige (mover, empujar, girar, etc.).</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+    <row r="18" ht="44.1" customHeight="1" s="28">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
-      <c r="F17" s="20" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Nivel de presión temporal percibida. Razón entre el tiempo necesario y el tiempo disponible para la ejecución de la tarea.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="B18" s="21" t="inlineStr">
+    <row r="19" ht="44.1" customHeight="1" s="28">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Muy bueno</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Muy malo</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F19" s="8" t="inlineStr">
         <is>
           <t>Medida en que el individuo se siente satisfecho con el rendimiento y desempeño de su trabajo.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+    <row r="20" ht="44.1" customHeight="1" s="28">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
-      <c r="F19" s="20" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Medida de esfuerzo físico y mental que el individuo precisa realizar para alcanzar su nivel de rendimiento.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="B20" s="21" t="inlineStr">
+    <row r="21" ht="44.1" customHeight="1" s="28">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F21" s="8" t="inlineStr">
         <is>
           <t>Nivel de inseguridad, estrés, irritación y otros sentimientos o estados negativos que el usuario experimenta durante la ejecución de la actividad.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23" ht="26.1" customHeight="1" s="28">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>Parte 2 · Comparaciones por pares</t>
         </is>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    </row>
+    <row r="25" ht="32.1" customHeight="1" s="28">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>Para cada par de mediciones que se muestran a continuación, elija entre las dos posibilidades la que considere que tuvo mayor impacto en la carga de trabajo que sintió al completar la tarea.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="26" ht="30" customHeight="1" s="28">
+      <c r="A26" s="43" t="inlineStr">
         <is>
           <t>En cada fila, elige en la lista cuál de las dos tuvo MAYOR impacto. Puedes revisar qué significa cada una en la tabla de la Parte 1.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="28" ht="32.1" customHeight="1" s="28">
+      <c r="A28" s="44" t="inlineStr">
         <is>
           <t>N.º</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>Opción A</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr"/>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="inlineStr">
         <is>
           <t>Opción B</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E28" s="44" t="inlineStr">
         <is>
           <t>Tu elección</t>
         </is>
       </c>
-      <c r="F27" s="24" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="25" t="n">
+      <c r="F28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="21.95" customHeight="1" s="28">
+      <c r="A29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
+      <c r="D29" s="10" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="28" t="n">
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="21.95" customHeight="1" s="28">
+      <c r="A30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="12" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="25" t="n">
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="21.95" customHeight="1" s="28">
+      <c r="A31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
+      <c r="D31" s="10" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="12" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="28" t="n">
+      <c r="E31" s="41" t="n"/>
+      <c r="F31" s="35" t="n"/>
+    </row>
+    <row r="32" ht="21.95" customHeight="1" s="28">
+      <c r="A32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D31" s="29" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="12" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="25" t="n">
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="21.95" customHeight="1" s="28">
+      <c r="A33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="12" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="28" t="n">
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="35" t="n"/>
+    </row>
+    <row r="34" ht="21.95" customHeight="1" s="28">
+      <c r="A34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D33" s="29" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="12" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="25" t="n">
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="21.95" customHeight="1" s="28">
+      <c r="A35" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
+      <c r="D35" s="10" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="12" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="28" t="n">
+      <c r="E35" s="41" t="n"/>
+      <c r="F35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="21.95" customHeight="1" s="28">
+      <c r="A36" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D35" s="29" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="12" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="25" t="n">
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="35" t="n"/>
+    </row>
+    <row r="37" ht="21.95" customHeight="1" s="28">
+      <c r="A37" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B37" s="10" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="12" t="n"/>
-    </row>
-    <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="28" t="n">
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="35" t="n"/>
+    </row>
+    <row r="38" ht="21.95" customHeight="1" s="28">
+      <c r="A38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D37" s="29" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>Frustración</t>
         </is>
       </c>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="12" t="n"/>
-    </row>
-    <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="25" t="n">
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="35" t="n"/>
+    </row>
+    <row r="39" ht="21.95" customHeight="1" s="28">
+      <c r="A39" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>Desempeño</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D39" s="10" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="12" t="n"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="28" t="n">
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="35" t="n"/>
+    </row>
+    <row r="40" ht="21.95" customHeight="1" s="28">
+      <c r="A40" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B40" s="13" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="C39" s="22" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D39" s="29" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="25" t="n">
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="35" t="n"/>
+    </row>
+    <row r="41" ht="21.95" customHeight="1" s="28">
+      <c r="A41" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="B41" s="10" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D41" s="10" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="12" t="n"/>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="28" t="n">
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="35" t="n"/>
+    </row>
+    <row r="42" ht="21.95" customHeight="1" s="28">
+      <c r="A42" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>Exigencia temporal</t>
         </is>
       </c>
-      <c r="C41" s="22" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D41" s="29" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Exigencia mental</t>
         </is>
       </c>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="12" t="n"/>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="25" t="n">
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="35" t="n"/>
+    </row>
+    <row r="43" ht="21.95" customHeight="1" s="28">
+      <c r="A43" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Esfuerzo</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>o</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D43" s="10" t="inlineStr">
         <is>
           <t>Exigencia física</t>
         </is>
       </c>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="12" t="n"/>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="28">
+    <mergeCell ref="E43:F43"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E42:F42"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="E39:F39"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="E35:F35"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="E40:F40"/>
     <mergeCell ref="E31:F31"/>
     <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A13:F13"/>
     <mergeCell ref="E36:F36"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="E32:F32"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="E37:F37"/>
-    <mergeCell ref="A7:F7"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <dataValidations count="16">
-    <dataValidation sqref="D15 D16 D17 D18 D19 D20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="D16 D17 D18 D19 D20 D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"0,5,10,15,20,25,30,35,40,45,50,55,60,65,70,75,80,85,90,95,100"</formula1>
     </dataValidation>
-    <dataValidation sqref="E28" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Esfuerzo,Desempeño"</formula1>
     </dataValidation>
-    <dataValidation sqref="E29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E30" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia temporal,Esfuerzo"</formula1>
     </dataValidation>
-    <dataValidation sqref="E30" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Desempeño,Frustración"</formula1>
     </dataValidation>
-    <dataValidation sqref="E31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E32" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia mental,Exigencia física"</formula1>
     </dataValidation>
-    <dataValidation sqref="E32" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E33" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia física,Desempeño"</formula1>
     </dataValidation>
-    <dataValidation sqref="E33" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Frustración,Esfuerzo"</formula1>
     </dataValidation>
-    <dataValidation sqref="E34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Desempeño,Exigencia temporal"</formula1>
     </dataValidation>
-    <dataValidation sqref="E35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia física,Frustración"</formula1>
     </dataValidation>
-    <dataValidation sqref="E36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E37" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Frustración,Exigencia mental"</formula1>
     </dataValidation>
-    <dataValidation sqref="E37" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia temporal,Frustración"</formula1>
     </dataValidation>
-    <dataValidation sqref="E38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Desempeño,Exigencia mental"</formula1>
     </dataValidation>
-    <dataValidation sqref="E39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E40" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia mental,Esfuerzo"</formula1>
     </dataValidation>
-    <dataValidation sqref="E40" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia física,Exigencia temporal"</formula1>
     </dataValidation>
-    <dataValidation sqref="E41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E42" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Exigencia temporal,Exigencia mental"</formula1>
     </dataValidation>
-    <dataValidation sqref="E42" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="E43" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"Esfuerzo,Exigencia física"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0000B050"/>
+    <tabColor rgb="FFB4A7D6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" style="28" min="1" max="1"/>
+    <col width="22" customWidth="1" style="28" min="2" max="2"/>
+    <col width="12" customWidth="1" style="28" min="3" max="3"/>
+    <col width="20" customWidth="1" style="28" min="4" max="4"/>
+    <col width="12" customWidth="1" style="28" min="5" max="5"/>
+    <col width="46" customWidth="1" style="28" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Opinión sobre el sistema</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Hoja 3 de 4 · SUS</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>Cuestionario NASA-TLX · Método 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Hoja 3 de 4 · Carga de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" s="28">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Cómo responder: haz clic en una celda amarilla y elige tu respuesta en la flecha ▼ que aparece a la derecha.</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Por favor seleccione de cada uno de los enunciados la opción que mejor describa su experiencia con la herramienta electrónica. Un puntaje de 1 significa que usted se encuentra totalmente en desacuerdo con el enunciado, mientras que un puntaje en 5 significa que está totalmente de acuerdo, un puntaje de 3 significaría que usted se encuentra neutral con el enunciado.</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="10" t="inlineStr">
-        <is>
-          <t>Qué significa cada número:</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="30" t="n">
+    </row>
+    <row r="5" ht="33.95" customHeight="1" s="28">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Responde pensando SOLO en la lectura con el Método 2: Ayuda a pedido: apareció el botón "Ver ayuda" y tú decidías si abrirla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="21.95" customHeight="1" s="28">
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>No pienses en las otras páginas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Cuestionario NASA-TLX aplicado al proyecto IRIS · Versión 3.0 — 29/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26.1" customHeight="1" s="28">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>Parte 1 · ¿Cuánto te exigió la tarea?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45.95" customHeight="1" s="28">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Por favor, lea cuidadosamente la descripción de cada dimensión y seleccione el nivel que mejor represente su experiencia durante la realización de la tarea. Preste especial atención al significado de cada extremo de la escala.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32.1" customHeight="1" s="28">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>La escala va de 0 a 100 en pasos de 5: 0 es el extremo izquierdo y 100 el derecho. Ojo: en «Desempeño» la escala va al revés (0 = Muy bueno, 100 = Muy malo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32.1" customHeight="1" s="28">
+      <c r="B15" s="44" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="C15" s="44" t="inlineStr">
+        <is>
+          <t>Si eliges 0</t>
+        </is>
+      </c>
+      <c r="D15" s="44" t="inlineStr">
+        <is>
+          <t>Tu nivel
+(0 a 100)</t>
+        </is>
+      </c>
+      <c r="E15" s="44" t="inlineStr">
+        <is>
+          <t>Si eliges 100</t>
+        </is>
+      </c>
+      <c r="F15" s="44" t="inlineStr">
+        <is>
+          <t>Qué significa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44.1" customHeight="1" s="28">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Muy bajo</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Cantidad de actividad mental y perceptiva que la tarea exige (decidir, pensar, calcular, procurar, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44.1" customHeight="1" s="28">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Muy bajo</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Cantidad de actividad física que la tarea exige (mover, empujar, girar, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44.1" customHeight="1" s="28">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Muy bajo</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Nivel de presión temporal percibida. Razón entre el tiempo necesario y el tiempo disponible para la ejecución de la tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44.1" customHeight="1" s="28">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Muy bueno</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Muy malo</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Medida en que el individuo se siente satisfecho con el rendimiento y desempeño de su trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44.1" customHeight="1" s="28">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Muy bajo</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Medida de esfuerzo físico y mental que el individuo precisa realizar para alcanzar su nivel de rendimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44.1" customHeight="1" s="28">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Muy bajo</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>Nivel de inseguridad, estrés, irritación y otros sentimientos o estados negativos que el usuario experimenta durante la ejecución de la actividad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26.1" customHeight="1" s="28">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Parte 2 · Comparaciones por pares</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32.1" customHeight="1" s="28">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>Para cada par de mediciones que se muestran a continuación, elija entre las dos posibilidades la que considere que tuvo mayor impacto en la carga de trabajo que sintió al completar la tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1" s="28">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>En cada fila, elige en la lista cuál de las dos tuvo MAYOR impacto. Puedes revisar qué significa cada una en la tabla de la Parte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32.1" customHeight="1" s="28">
+      <c r="A28" s="44" t="inlineStr">
+        <is>
+          <t>N.º</t>
+        </is>
+      </c>
+      <c r="B28" s="44" t="inlineStr">
+        <is>
+          <t>Opción A</t>
+        </is>
+      </c>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="inlineStr">
+        <is>
+          <t>Opción B</t>
+        </is>
+      </c>
+      <c r="E28" s="44" t="inlineStr">
+        <is>
+          <t>Tu elección</t>
+        </is>
+      </c>
+      <c r="F28" s="45" t="n"/>
+    </row>
+    <row r="29" ht="21.95" customHeight="1" s="28">
+      <c r="A29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="31" t="inlineStr">
-        <is>
-          <t>Totalmente en desacuerdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="32" t="n">
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="n"/>
+      <c r="F29" s="35" t="n"/>
+    </row>
+    <row r="30" ht="21.95" customHeight="1" s="28">
+      <c r="A30" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>En desacuerdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="34" t="n">
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="n"/>
+      <c r="F30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="21.95" customHeight="1" s="28">
+      <c r="A31" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="35" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="36" t="n">
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="E31" s="41" t="n"/>
+      <c r="F31" s="35" t="n"/>
+    </row>
+    <row r="32" ht="21.95" customHeight="1" s="28">
+      <c r="A32" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
-        <is>
-          <t>De acuerdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="38" t="n">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="E32" s="41" t="n"/>
+      <c r="F32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="21.95" customHeight="1" s="28">
+      <c r="A33" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="39" t="inlineStr">
-        <is>
-          <t>Totalmente de acuerdo</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t>N.º</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Enunciado</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>Tu respuesta</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
-        <is>
-          <t>Me gustaría usar esta herramienta frecuentemente.</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="n"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="41" t="inlineStr">
-        <is>
-          <t>Considero que esta herramienta es innecesariamente compleja</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="n"/>
-    </row>
-    <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="40" t="inlineStr">
-        <is>
-          <t>Considero que la herramienta es fácil de usar.</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="n"/>
-    </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="41" t="inlineStr">
-        <is>
-          <t>Considero necesario el apoyo de personal experto para poder utilizar esta herramienta</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="40" t="inlineStr">
-        <is>
-          <t>Considero que las funciones de la herramienta están bien integradas</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="n"/>
-    </row>
-    <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="28" t="n">
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="n"/>
+      <c r="F33" s="35" t="n"/>
+    </row>
+    <row r="34" ht="21.95" customHeight="1" s="28">
+      <c r="A34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="41" t="inlineStr">
-        <is>
-          <t>Considero que la herramienta presenta muchas contradicciones</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="n"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="25" t="n">
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="E34" s="41" t="n"/>
+      <c r="F34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="21.95" customHeight="1" s="28">
+      <c r="A35" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B21" s="40" t="inlineStr">
-        <is>
-          <t>Imagino que la mayoría de las personas aprenderían a usar esta herramienta rápidamente</t>
-        </is>
-      </c>
-      <c r="C21" s="27" t="n"/>
-    </row>
-    <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="28" t="n">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="n"/>
+      <c r="F35" s="35" t="n"/>
+    </row>
+    <row r="36" ht="21.95" customHeight="1" s="28">
+      <c r="A36" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B22" s="41" t="inlineStr">
-        <is>
-          <t>Considero que el uso de esta herramienta es tedioso</t>
-        </is>
-      </c>
-      <c r="C22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="25" t="n">
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="n"/>
+      <c r="F36" s="35" t="n"/>
+    </row>
+    <row r="37" ht="21.95" customHeight="1" s="28">
+      <c r="A37" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B23" s="40" t="inlineStr">
-        <is>
-          <t>Me sentí muy confiado al usar la herramienta</t>
-        </is>
-      </c>
-      <c r="C23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="28" t="n">
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="E37" s="41" t="n"/>
+      <c r="F37" s="35" t="n"/>
+    </row>
+    <row r="38" ht="21.95" customHeight="1" s="28">
+      <c r="A38" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="41" t="inlineStr">
-        <is>
-          <t>Necesité saber bastantes cosas antes de poder empezar a usar esta herramienta</t>
-        </is>
-      </c>
-      <c r="C24" s="27" t="n"/>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Frustración</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="n"/>
+      <c r="F38" s="35" t="n"/>
+    </row>
+    <row r="39" ht="21.95" customHeight="1" s="28">
+      <c r="A39" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Desempeño</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="n"/>
+      <c r="F39" s="35" t="n"/>
+    </row>
+    <row r="40" ht="21.95" customHeight="1" s="28">
+      <c r="A40" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B40" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="n"/>
+      <c r="F40" s="35" t="n"/>
+    </row>
+    <row r="41" ht="21.95" customHeight="1" s="28">
+      <c r="A41" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="n"/>
+      <c r="F41" s="35" t="n"/>
+    </row>
+    <row r="42" ht="21.95" customHeight="1" s="28">
+      <c r="A42" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="B42" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia temporal</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="inlineStr">
+        <is>
+          <t>Exigencia mental</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="n"/>
+      <c r="F42" s="35" t="n"/>
+    </row>
+    <row r="43" ht="21.95" customHeight="1" s="28">
+      <c r="A43" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Esfuerzo</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>o</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Exigencia física</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="n"/>
+      <c r="F43" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="28">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="C15 C16 C17 C18 C19 C20 C21 C22 C23 C24" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
-      <formula1>"1 = Totalmente en desacuerdo,2 = En desacuerdo,3 = Neutral,4 = De acuerdo,5 = Totalmente de acuerdo"</formula1>
+  <dataValidations count="16">
+    <dataValidation sqref="D16 D17 D18 D19 D20 D21" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"0,5,10,15,20,25,30,35,40,45,50,55,60,65,70,75,80,85,90,95,100"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E29" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Esfuerzo,Desempeño"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E30" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia temporal,Esfuerzo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Desempeño,Frustración"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E32" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia mental,Exigencia física"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E33" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia física,Desempeño"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E34" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Frustración,Esfuerzo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E35" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Desempeño,Exigencia temporal"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E36" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia física,Frustración"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E37" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Frustración,Exigencia mental"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E38" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia temporal,Frustración"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E39" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Desempeño,Exigencia mental"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E40" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia mental,Esfuerzo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E41" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia física,Exigencia temporal"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E42" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Exigencia temporal,Exigencia mental"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E43" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+      <formula1>"Esfuerzo,Exigencia física"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup fitToHeight="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00C55A11"/>
+    <tabColor rgb="FFC55A11"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="58" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" style="28" min="1" max="1"/>
+    <col width="58" customWidth="1" style="28" min="2" max="2"/>
+    <col width="22" customWidth="1" style="28" min="3" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="36" customHeight="1" s="28">
+      <c r="A1" s="37" t="inlineStr">
         <is>
           <t>Cuestionario post-experimento</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+    </row>
+    <row r="2" ht="20.1" customHeight="1" s="28">
+      <c r="A2" s="39" t="inlineStr">
         <is>
           <t>Hoja 4 de 4 · Comparación de los dos métodos</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Basado en el Anexo 4 del protocolo (v3.0, 29/09/2026), adaptado a la lectura</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5" ht="30" customHeight="1" s="28">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Cómo responder: haz clic en una celda amarilla y elige tu respuesta en la flecha ▼ que aparece a la derecha. En los comentarios, escribe directamente en el recuadro.</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+    </row>
+    <row r="6" ht="20.1" customHeight="1" s="28">
+      <c r="A6" s="38" t="inlineStr">
         <is>
           <t>Los dos métodos que usaste:</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+    </row>
+    <row r="7" ht="21.95" customHeight="1" s="28">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Método 1: Ayuda automática: la ayuda apareció sola cuando el sistema detectó que te costaba leer.</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+    </row>
+    <row r="8" ht="21.95" customHeight="1" s="28">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>Método 2: Ayuda a pedido: apareció el botón "Ver ayuda" y tú decidías si abrirla.</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    </row>
+    <row r="11" ht="26.1" customHeight="1" s="28">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>Ordena los métodos</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>Qué significa cada número:</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="30" t="n">
+    <row r="14" ht="20.1" customHeight="1" s="28">
+      <c r="A14" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Primer lugar</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="38" t="n">
+    <row r="15" ht="20.1" customHeight="1" s="28">
+      <c r="A15" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Segundo lugar</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>Considerando los 2 métodos, ¿con cuál la ayuda llegó en mejor momento? Por favor, ordénalos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="B18" s="43" t="inlineStr">
+    <row r="17" ht="30" customHeight="1" s="28" thickBot="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Considerando los 2 métodos de asistencia IA, ¿Cuál te permitió obtener ayuda más rápidamente? Por favor, ordénalos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Método 1</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="B19" s="43" t="inlineStr">
+      <c r="C18" s="41" t="n"/>
+    </row>
+    <row r="19" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Método 2</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>¿Cuál te resultó más cómodo (en orden)?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="B22" s="43" t="inlineStr">
+      <c r="C19" s="41" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1" s="28" thickBot="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>¿Cuál te resultó más cómodo? Por favor, ordénalos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Método 1</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="43" t="inlineStr">
+      <c r="C22" s="41" t="n"/>
+    </row>
+    <row r="23" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Método 2</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n"/>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>¿Con cuál método entendiste mejor el contenido (en orden)?</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="43" t="inlineStr">
+      <c r="C23" s="41" t="n"/>
+    </row>
+    <row r="25" ht="30" customHeight="1" s="28" thickBot="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>¿Con cuál sentiste mayor control? Por favor, ordénalos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Método 1</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="43" t="inlineStr">
+      <c r="C26" s="41" t="n"/>
+    </row>
+    <row r="27" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Método 2</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="42" t="inlineStr">
-        <is>
-          <t>Si tuvieras que leer textos difíciles con un solo método, ¿cuál elegirías? Por favor, ordena:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="B30" s="43" t="inlineStr">
+      <c r="C27" s="41" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1" s="28" thickBot="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>Si tuvieras que usar un solo método, ¿cuál elegirías para usar habitualmente? Por favor, ordénalos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Método 1</t>
         </is>
       </c>
-      <c r="C30" s="27" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="B31" s="43" t="inlineStr">
+      <c r="C30" s="41" t="n"/>
+    </row>
+    <row r="31" ht="20.1" customHeight="1" s="28" thickBot="1">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Método 2</t>
         </is>
       </c>
-      <c r="C31" s="27" t="n"/>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="C31" s="41" t="n"/>
+    </row>
+    <row r="34" ht="26.1" customHeight="1" s="28">
+      <c r="A34" s="32" t="inlineStr">
         <is>
           <t>Califica cada método de 1 a 5</t>
         </is>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="31" t="inlineStr">
         <is>
           <t>Qué significa cada número:</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="30" t="n">
+    <row r="37" ht="20.1" customHeight="1" s="28">
+      <c r="A37" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B37" s="31" t="inlineStr">
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>Muy bajo</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="32" t="n">
+    <row r="38" ht="20.1" customHeight="1" s="28">
+      <c r="A38" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Bajo</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="34" t="n">
+    <row r="39" ht="20.1" customHeight="1" s="28">
+      <c r="A39" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="22" t="inlineStr">
         <is>
           <t>Medio</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="36" t="n">
+    <row r="40" ht="20.1" customHeight="1" s="28">
+      <c r="A40" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B40" s="37" t="inlineStr">
+      <c r="B40" s="24" t="inlineStr">
         <is>
           <t>Alto</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="38" t="n">
+    <row r="41" ht="20.1" customHeight="1" s="28">
+      <c r="A41" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" s="17" t="inlineStr">
         <is>
           <t>Muy alto</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="32" customHeight="1">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="43" ht="32.1" customHeight="1" s="28">
+      <c r="A43" s="44" t="inlineStr">
         <is>
           <t>N.º</t>
         </is>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="44" t="inlineStr">
         <is>
           <t>Pregunta</t>
         </is>
       </c>
-      <c r="C43" s="16" t="inlineStr">
+      <c r="C43" s="44" t="inlineStr">
         <is>
           <t>Método 1
 (automática)</t>
         </is>
       </c>
-      <c r="D43" s="16" t="inlineStr">
+      <c r="D43" s="44" t="inlineStr">
         <is>
           <t>Método 2
 (a pedido)</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="25" t="n">
+    <row r="44" ht="33.95" customHeight="1" s="28">
+      <c r="A44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B44" s="40" t="inlineStr">
-        <is>
-          <t>¿En qué medida el método te ayudó a entender el texto?</t>
-        </is>
-      </c>
-      <c r="C44" s="27" t="n"/>
-      <c r="D44" s="27" t="n"/>
-    </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="28" t="n">
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>¿En qué medida este método te ayudó a completar la tarea?</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="n"/>
+      <c r="D44" s="41" t="n"/>
+    </row>
+    <row r="45" ht="33.95" customHeight="1" s="28">
+      <c r="A45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B45" s="41" t="inlineStr">
-        <is>
-          <t>¿Qué tan útiles fueron las explicaciones que recibiste?</t>
-        </is>
-      </c>
-      <c r="C45" s="27" t="n"/>
-      <c r="D45" s="27" t="n"/>
-    </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="25" t="n">
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>¿Qué nivel de comodidad y agrado te produjo interactuar con la asistencia de este método?</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="n"/>
+      <c r="D45" s="41" t="n"/>
+    </row>
+    <row r="46" ht="33.95" customHeight="1" s="28">
+      <c r="A46" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="B46" s="40" t="inlineStr">
-        <is>
-          <t>¿Qué tan agradable fue leer con este método?</t>
-        </is>
-      </c>
-      <c r="C46" s="27" t="n"/>
-      <c r="D46" s="27" t="n"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="28" t="n">
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>¿Qué nivel de facilidad tuviste para aprender a usar este método?</t>
+        </is>
+      </c>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="41" t="n"/>
+    </row>
+    <row r="47" ht="33.95" customHeight="1" s="28">
+      <c r="A47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B47" s="41" t="inlineStr">
-        <is>
-          <t>¿Qué tan fácil fue aprender a utilizar este método?</t>
-        </is>
-      </c>
-      <c r="C47" s="27" t="n"/>
-      <c r="D47" s="27" t="n"/>
-    </row>
-    <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="25" t="n">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>¿Qué nivel de rapidez percibiste para obtener la ayuda cuando la necesitaste?</t>
+        </is>
+      </c>
+      <c r="C47" s="41" t="n"/>
+      <c r="D47" s="41" t="n"/>
+    </row>
+    <row r="48" ht="33.95" customHeight="1" s="28">
+      <c r="A48" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B48" s="40" t="inlineStr">
-        <is>
-          <t>¿Con qué frecuencia la ayuda apareció cuando de verdad la necesitabas?</t>
-        </is>
-      </c>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="27" t="n"/>
-    </row>
-    <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="28" t="n">
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>¿Qué nivel de precisión percibiste en la ayuda respecto al contenido que estabas consultando?</t>
+        </is>
+      </c>
+      <c r="C48" s="41" t="n"/>
+      <c r="D48" s="41" t="n"/>
+    </row>
+    <row r="49" ht="33.95" customHeight="1" s="28">
+      <c r="A49" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B49" s="41" t="inlineStr">
-        <is>
-          <t>¿Qué nivel de confianza sentiste al utilizar este método?</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="27" t="n"/>
-    </row>
-    <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="25" t="n">
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>¿Qué nivel de confianza sentiste en la información proporcionada por la ayuda?</t>
+        </is>
+      </c>
+      <c r="C49" s="41" t="n"/>
+      <c r="D49" s="41" t="n"/>
+    </row>
+    <row r="50" ht="33.95" customHeight="1" s="28" thickBot="1">
+      <c r="A50" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B50" s="40" t="inlineStr">
-        <is>
-          <t>¿Qué tan dispuesto(a) estarías a utilizar este método en tu vida diaria al leer en internet?</t>
-        </is>
-      </c>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="27" t="n"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="B51" s="41" t="inlineStr">
-        <is>
-          <t>¿Qué tanto te distrajo o interrumpió la ayuda?</t>
-        </is>
-      </c>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="27" t="n"/>
-    </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>¿Qué tan dispuesto/a estarías a utilizar este método en tareas similares en el futuro?</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="n"/>
+      <c r="D50" s="41" t="n"/>
+    </row>
+    <row r="52" ht="26.1" customHeight="1" s="28">
+      <c r="A52" s="32" t="inlineStr">
         <is>
           <t>Comentarios finales</t>
         </is>
       </c>
-      <c r="B53" s="9" t="n"/>
-      <c r="C53" s="9" t="n"/>
-      <c r="D53" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>¿Qué aspectos positivos encontraste en cada método?</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="70" customHeight="1">
-      <c r="A56" s="11" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
+    </row>
+    <row r="54" ht="15" customHeight="1" s="28" thickBot="1">
+      <c r="A54" s="36" t="inlineStr">
+        <is>
+          <t>¿Qué aspectos positivos encontraste en cada técnica?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="69.95" customHeight="1" s="28" thickBot="1">
+      <c r="A55" s="33" t="n"/>
+      <c r="B55" s="34" t="n"/>
+      <c r="C55" s="34" t="n"/>
+      <c r="D55" s="35" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
         <is>
           <t>¿Qué dificultades encontraste?</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="70" customHeight="1">
-      <c r="A59" s="11" t="n"/>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="10" t="inlineStr">
-        <is>
-          <t>¿Tienes alguna sugerencia para mejorar los métodos evaluados?</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="70" customHeight="1">
-      <c r="A62" s="11" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
+    <row r="58" ht="69.95" customHeight="1" s="28">
+      <c r="A58" s="33" t="n"/>
+      <c r="B58" s="34" t="n"/>
+      <c r="C58" s="34" t="n"/>
+      <c r="D58" s="35" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="28" thickBot="1">
+      <c r="A60" s="36" t="inlineStr">
+        <is>
+          <t>¿Tienes alguna sugerencia para mejorar las técnicas evaluadas?</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="69.95" customHeight="1" s="28" thickBot="1">
+      <c r="A61" s="33" t="n"/>
+      <c r="B61" s="34" t="n"/>
+      <c r="C61" s="34" t="n"/>
+      <c r="D61" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A17:D17"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A53:D53"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A52:D52"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="A58:D58"/>
     <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A59:D59"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B36:D36"/>
     <mergeCell ref="A61:D61"/>
     <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A56:D56"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="C18 C19 C22 C23 C26 C27 C30 C31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+  <dataValidations count="3">
+    <dataValidation sqref="C18:C19 C22:C23 C26:C27 C30:C31" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"1 = Primer lugar,2 = Segundo lugar"</formula1>
     </dataValidation>
-    <dataValidation sqref="C44 C45 C46 C47 C48 C49 C50 C51 D44 D45 D46 D47 D48 D49 D50 D51" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
+    <dataValidation sqref="C44:D45 C47:D50" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Respuesta no válida" error="Elige una opción de la lista." promptTitle="Elige una opción" prompt="Usa la flecha ▼ de la derecha." type="list">
       <formula1>"1 = Muy bajo,2 = Bajo,3 = Medio,4 = Alto,5 = Muy alto"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46:D46" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Respuesta no válida" error="En esta pregunta solo se puede elegir 1 o 5." promptTitle="Elige una opción" prompt="Solo 1 (Muy bajo) o 5 (Muy alto). Usa la flecha ▼." type="list">
+      <formula1>"1 = Muy bajo,5 = Muy alto"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <pageSetup fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -2347,8 +2770,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C62"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C71"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2375,7 +2798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>resumen_facil</t>
+          <t>resumen_pos1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2392,7 +2815,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>resumen_intermedio</t>
+          <t>resumen_pos2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2409,7 +2832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>resumen_avanzado</t>
+          <t>resumen_pos3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2421,7 +2844,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2431,14 +2854,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>D15</t>
+          <t>D16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2448,14 +2871,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>D16</t>
+          <t>D17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2465,14 +2888,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>D17</t>
+          <t>D18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2482,14 +2905,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D18</t>
+          <t>D19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2499,14 +2922,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>D19</t>
+          <t>D20</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2516,14 +2939,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>D20</t>
+          <t>D21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2533,14 +2956,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>E28</t>
+          <t>E29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2550,14 +2973,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>E29</t>
+          <t>E30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2567,14 +2990,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>E30</t>
+          <t>E31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2584,14 +3007,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>E31</t>
+          <t>E32</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2601,14 +3024,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>E32</t>
+          <t>E33</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2618,14 +3041,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>E33</t>
+          <t>E34</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2635,14 +3058,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>E34</t>
+          <t>E35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2652,14 +3075,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>E35</t>
+          <t>E36</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2669,14 +3092,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>E36</t>
+          <t>E37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2686,14 +3109,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>E37</t>
+          <t>E38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2703,14 +3126,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>E38</t>
+          <t>E39</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2720,14 +3143,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>E39</t>
+          <t>E40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2737,14 +3160,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>E40</t>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2754,14 +3177,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>E41</t>
+          <t>E42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NASA-TLX</t>
+          <t>NASA-TLX Método 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2771,364 +3194,364 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>E42</t>
+          <t>E43</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>sus_1</t>
+          <t>nasa_mental</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C15</t>
+          <t>D16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>sus_2</t>
+          <t>nasa_fisica</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>C16</t>
+          <t>D17</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sus_3</t>
+          <t>nasa_temporal</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>D18</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sus_4</t>
+          <t>nasa_desempeno</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>D19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>sus_5</t>
+          <t>nasa_esfuerzo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>D20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sus_6</t>
+          <t>nasa_frustracion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>C20</t>
+          <t>D21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>sus_7</t>
+          <t>par_01</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>E29</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sus_8</t>
+          <t>par_02</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>E30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sus_9</t>
+          <t>par_03</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>E31</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SUS</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>sus_10</t>
+          <t>par_04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>E32</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>orden_momento_m1</t>
+          <t>par_05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>E33</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>orden_momento_m2</t>
+          <t>par_06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>C19</t>
+          <t>E34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>orden_comodo_m1</t>
+          <t>par_07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>E35</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>orden_comodo_m2</t>
+          <t>par_08</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>C23</t>
+          <t>E36</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>orden_comprension_m1</t>
+          <t>par_09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>E37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>orden_comprension_m2</t>
+          <t>par_10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>E38</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>orden_elegiria_m1</t>
+          <t>par_11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C30</t>
+          <t>E39</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>orden_elegiria_m2</t>
+          <t>par_12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>E40</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>califica_entender_m1</t>
+          <t>par_13</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>C44</t>
+          <t>E41</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>califica_entender_m2</t>
+          <t>par_14</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>D44</t>
+          <t>E42</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Post-experimento</t>
+          <t>NASA-TLX Método 2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>califica_utilidad_m1</t>
+          <t>par_15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>C45</t>
+          <t>E43</t>
         </is>
       </c>
     </row>
@@ -3140,12 +3563,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>califica_utilidad_m2</t>
+          <t>orden_rapidez_m1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>D45</t>
+          <t>C18</t>
         </is>
       </c>
     </row>
@@ -3157,12 +3580,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>califica_agradable_m1</t>
+          <t>orden_rapidez_m2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>C46</t>
+          <t>C19</t>
         </is>
       </c>
     </row>
@@ -3174,12 +3597,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>califica_agradable_m2</t>
+          <t>orden_comodo_m1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>D46</t>
+          <t>C22</t>
         </is>
       </c>
     </row>
@@ -3191,12 +3614,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>califica_aprender_m1</t>
+          <t>orden_comodo_m2</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>C47</t>
+          <t>C23</t>
         </is>
       </c>
     </row>
@@ -3208,12 +3631,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>califica_aprender_m2</t>
+          <t>orden_control_m1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>D47</t>
+          <t>C26</t>
         </is>
       </c>
     </row>
@@ -3225,12 +3648,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>califica_oportuna_m1</t>
+          <t>orden_control_m2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>C48</t>
+          <t>C27</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3665,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>califica_oportuna_m2</t>
+          <t>orden_elegiria_m1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>D48</t>
+          <t>C30</t>
         </is>
       </c>
     </row>
@@ -3259,12 +3682,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>califica_confianza_m1</t>
+          <t>orden_elegiria_m2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>C49</t>
+          <t>C31</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3699,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>califica_confianza_m2</t>
+          <t>califica_completar_m1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>D49</t>
+          <t>C44</t>
         </is>
       </c>
     </row>
@@ -3293,12 +3716,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>califica_vida_diaria_m1</t>
+          <t>califica_completar_m2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>C50</t>
+          <t>D44</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3733,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>califica_vida_diaria_m2</t>
+          <t>califica_comodidad_m1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>D50</t>
+          <t>C45</t>
         </is>
       </c>
     </row>
@@ -3327,12 +3750,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>califica_distraccion_m1</t>
+          <t>califica_comodidad_m2</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>C51</t>
+          <t>D45</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3767,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>califica_distraccion_m2</t>
+          <t>califica_aprender_m1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>D51</t>
+          <t>C46</t>
         </is>
       </c>
     </row>
@@ -3361,12 +3784,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>comentario_positivos</t>
+          <t>califica_aprender_m2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A56</t>
+          <t>D46</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3801,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>comentario_dificultades</t>
+          <t>califica_rapidez_m1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A59</t>
+          <t>C47</t>
         </is>
       </c>
     </row>
@@ -3395,12 +3818,165 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
+          <t>califica_rapidez_m2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>D47</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>califica_precision_m1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C48</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>califica_precision_m2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>D48</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>califica_confianza_m1</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>C49</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>califica_confianza_m2</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>D49</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>califica_futuro_m1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>C50</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>califica_futuro_m2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>D50</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>comentario_positivos</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>A55</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>comentario_dificultades</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A58</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Post-experimento</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>comentario_sugerencias</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>A62</t>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>A61</t>
         </is>
       </c>
     </row>
